--- a/tests/testdata/excel/ファイル名/A.xlsx_old.xlsx
+++ b/tests/testdata/excel/ファイル名/A.xlsx_old.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB96BAC5-AA2F-4857-8F83-D7A1C14EBD34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FF89EBFB-22B2-4E9C-B7B2-C6A0B606D6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{A0C033CA-9AF4-4E10-BC5B-B7DA041E6950}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{EA5DCE8F-FC5E-4017-BE96-A738BB2B77DD}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F27AFE7D-9432-4240-B404-0751E2882FC1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B9A0EA-BDDE-41CC-B645-336E5368CBBF}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
